--- a/frontend/public/forms/templates/ics-template.xlsx
+++ b/frontend/public/forms/templates/ics-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GIO\Desktop\CHERIE\CAPSTONE\frontend\public\forms\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4809CF44-10DE-47F5-91A4-AE59877C8287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC366D8-5673-4BF1-BA81-3EDC77F4C209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ICS" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,12 +125,6 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -152,21 +146,8 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <i/>
       <sz val="14"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -179,10 +160,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -507,7 +524,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -518,205 +535,206 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1010,656 +1028,708 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H1" s="66" t="s">
+      <c r="H1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="66"/>
+      <c r="I1" s="12"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
       <c r="J3" s="2"/>
       <c r="K3" s="3"/>
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="54"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
       <c r="J4" s="2"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+    <row r="5" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
       <c r="J5" s="2"/>
       <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:11" s="5" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="16"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="18"/>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="18" t="s">
+      <c r="B7" s="21"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="70"/>
+      <c r="I7" s="23"/>
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:11" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="24"/>
       <c r="B8" s="25"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
     </row>
     <row r="9" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="59"/>
-      <c r="E9" s="60" t="s">
+      <c r="D9" s="28"/>
+      <c r="E9" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="75"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="64" t="s">
+      <c r="F9" s="30"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="55" t="s">
+      <c r="I9" s="26" t="s">
         <v>7</v>
       </c>
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="56"/>
-      <c r="B10" s="56"/>
-      <c r="C10" s="48" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="D10" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="62"/>
-      <c r="F10" s="76"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="65"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
       <c r="J10" s="6"/>
     </row>
     <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="57"/>
-      <c r="B11" s="56"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
+      <c r="A11" s="40"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
       <c r="J11" s="6"/>
     </row>
     <row r="12" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
+      <c r="A12" s="42"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
     </row>
     <row r="13" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
+      <c r="A13" s="42"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
     </row>
     <row r="14" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
+      <c r="A14" s="42"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
     </row>
     <row r="15" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
+      <c r="A15" s="42"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
     </row>
     <row r="16" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
+      <c r="A16" s="42"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
     </row>
     <row r="17" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
+      <c r="A17" s="42"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
     </row>
     <row r="18" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
+      <c r="A18" s="42"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
     </row>
     <row r="19" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
     </row>
     <row r="20" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
+      <c r="A20" s="42"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
     </row>
     <row r="21" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
+      <c r="A21" s="42"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
     </row>
     <row r="22" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
+      <c r="A22" s="42"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
     </row>
     <row r="23" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
+      <c r="A23" s="42"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
     </row>
     <row r="24" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
+      <c r="A24" s="42"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
     </row>
     <row r="25" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
+      <c r="A25" s="42"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
     </row>
     <row r="26" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="77"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
+      <c r="A26" s="42"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
     </row>
     <row r="27" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
+      <c r="A27" s="42"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
     </row>
     <row r="28" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="26"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="77"/>
-      <c r="G28" s="52"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
+      <c r="A28" s="42"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
     </row>
     <row r="29" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="26"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="77"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
+      <c r="A29" s="42"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
     </row>
     <row r="30" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="77"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
+      <c r="A30" s="42"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
     </row>
     <row r="31" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="26"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="77"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
+      <c r="A31" s="42"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
     </row>
     <row r="32" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="26"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="77"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
+      <c r="A32" s="42"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="26"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
+      <c r="A33" s="42"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="26"/>
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="77"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
+      <c r="A34" s="42"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="26"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
+      <c r="A35" s="42"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="26"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
+      <c r="A36" s="42"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="26"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
+      <c r="A37" s="42"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="26"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
+      <c r="A38" s="42"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="26"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="52"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
+      <c r="A39" s="42"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="26"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
+      <c r="A40" s="42"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="23" t="s">
+      <c r="A41" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="50"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="53"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="49"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="68" t="s">
+      <c r="A42" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="B42" s="37"/>
-      <c r="C42" s="38"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="39"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="57"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="20"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="42"/>
+      <c r="A43" s="54"/>
+      <c r="B43" s="58"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="60"/>
     </row>
     <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="21"/>
-      <c r="B44" s="43"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="44"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="45"/>
+      <c r="A44" s="61"/>
+      <c r="B44" s="62"/>
+      <c r="C44" s="63"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="63"/>
+      <c r="I44" s="64"/>
     </row>
     <row r="45" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="8" t="s">
+      <c r="B45" s="65"/>
+      <c r="C45" s="65"/>
+      <c r="D45" s="65"/>
+      <c r="E45" s="66"/>
+      <c r="F45" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="9"/>
+      <c r="G45" s="65"/>
+      <c r="H45" s="65"/>
+      <c r="I45" s="66"/>
     </row>
     <row r="46" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="10"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="78"/>
-      <c r="G46" s="78"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="11"/>
+      <c r="A46" s="67"/>
+      <c r="B46" s="68"/>
+      <c r="C46" s="68"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="68"/>
+      <c r="H46" s="68"/>
+      <c r="I46" s="69"/>
     </row>
     <row r="47" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="71"/>
-      <c r="B47" s="80"/>
-      <c r="C47" s="80"/>
-      <c r="D47" s="80"/>
+      <c r="A47" s="70"/>
+      <c r="B47" s="71"/>
+      <c r="C47" s="71"/>
+      <c r="D47" s="71"/>
       <c r="E47" s="72"/>
-      <c r="F47" s="79"/>
-      <c r="G47" s="80"/>
-      <c r="H47" s="80"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="71"/>
+      <c r="H47" s="71"/>
       <c r="I47" s="72"/>
-      <c r="J47" s="12"/>
+      <c r="J47" s="7"/>
     </row>
     <row r="48" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="73"/>
-      <c r="C48" s="73"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="30" t="s">
+      <c r="B48" s="75"/>
+      <c r="C48" s="75"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="76"/>
+      <c r="F48" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="G48" s="73"/>
-      <c r="H48" s="73"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="12"/>
+      <c r="G48" s="75"/>
+      <c r="H48" s="75"/>
+      <c r="I48" s="76"/>
+      <c r="J48" s="7"/>
     </row>
     <row r="49" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="71"/>
-      <c r="B49" s="80"/>
-      <c r="C49" s="80"/>
-      <c r="D49" s="80"/>
+      <c r="A49" s="70"/>
+      <c r="B49" s="71"/>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
       <c r="E49" s="72"/>
-      <c r="F49" s="71"/>
-      <c r="G49" s="80"/>
-      <c r="H49" s="80"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
       <c r="I49" s="72"/>
-      <c r="J49" s="12"/>
+      <c r="J49" s="7"/>
     </row>
     <row r="50" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="73"/>
-      <c r="C50" s="73"/>
-      <c r="D50" s="73"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="30" t="s">
+      <c r="B50" s="75"/>
+      <c r="C50" s="75"/>
+      <c r="D50" s="75"/>
+      <c r="E50" s="76"/>
+      <c r="F50" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="G50" s="73"/>
-      <c r="H50" s="73"/>
-      <c r="I50" s="31"/>
-      <c r="J50" s="12"/>
+      <c r="G50" s="75"/>
+      <c r="H50" s="75"/>
+      <c r="I50" s="76"/>
+      <c r="J50" s="7"/>
     </row>
     <row r="51" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="71"/>
-      <c r="B51" s="80"/>
-      <c r="C51" s="80"/>
-      <c r="D51" s="80"/>
+      <c r="A51" s="70"/>
+      <c r="B51" s="71"/>
+      <c r="C51" s="71"/>
+      <c r="D51" s="71"/>
       <c r="E51" s="72"/>
-      <c r="F51" s="71"/>
-      <c r="G51" s="80"/>
-      <c r="H51" s="80"/>
+      <c r="F51" s="70"/>
+      <c r="G51" s="71"/>
+      <c r="H51" s="71"/>
       <c r="I51" s="72"/>
-      <c r="J51" s="12"/>
+      <c r="J51" s="7"/>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="32" t="s">
+      <c r="A52" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="B52" s="33"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="33"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="32" t="s">
+      <c r="B52" s="78"/>
+      <c r="C52" s="78"/>
+      <c r="D52" s="78"/>
+      <c r="E52" s="79"/>
+      <c r="F52" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="G52" s="33"/>
-      <c r="H52" s="33"/>
-      <c r="I52" s="34"/>
-      <c r="J52" s="12"/>
+      <c r="G52" s="78"/>
+      <c r="H52" s="78"/>
+      <c r="I52" s="79"/>
+      <c r="J52" s="7"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
+      <c r="A53" s="8"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="14"/>
+      <c r="A54" s="9"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="15"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="15"/>
+      <c r="A58" s="10"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" s="29"/>
-      <c r="B110" s="29"/>
-      <c r="C110" s="29"/>
-      <c r="D110" s="29"/>
-      <c r="E110" s="29"/>
-      <c r="F110" s="29"/>
-      <c r="G110" s="29"/>
-      <c r="H110" s="29"/>
-      <c r="I110" s="29"/>
+      <c r="A110" s="15"/>
+      <c r="B110" s="15"/>
+      <c r="C110" s="15"/>
+      <c r="D110" s="15"/>
+      <c r="E110" s="15"/>
+      <c r="F110" s="15"/>
+      <c r="G110" s="15"/>
+      <c r="H110" s="15"/>
+      <c r="I110" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="A110:I110"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="A3:I4"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:G11"/>
+    <mergeCell ref="H9:H11"/>
+    <mergeCell ref="I9:I11"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="E33:G33"/>
     <mergeCell ref="E34:G34"/>
@@ -1676,50 +1746,6 @@
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I4"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:G11"/>
-    <mergeCell ref="H9:H11"/>
-    <mergeCell ref="I9:I11"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="B42:I42"/>
-    <mergeCell ref="B43:I43"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="A110:I110"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="G49:H49"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="1.25" right="1" top="1" bottom="0.5" header="0" footer="0.5"/>
